--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Quant Fund.xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Quant Fund.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="569" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="178">
   <si>
     <t>ICICI Prudential Mutual Fund</t>
   </si>
@@ -22,7 +22,7 @@
     <t>ICICI Prudential Quant Fund</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -61,19 +61,298 @@
     <t>Listed / Awaiting Listing On Stock Exchanges</t>
   </si>
   <si>
+    <t>ACC Ltd.</t>
+  </si>
+  <si>
+    <t>INE012A01025</t>
+  </si>
+  <si>
+    <t>Cement &amp; Cement Products</t>
+  </si>
+  <si>
+    <t>Bharti Airtel Ltd.</t>
+  </si>
+  <si>
+    <t>INE397D01024</t>
+  </si>
+  <si>
+    <t>Telecom - Services</t>
+  </si>
+  <si>
+    <t>ITC Ltd.</t>
+  </si>
+  <si>
+    <t>INE154A01025</t>
+  </si>
+  <si>
+    <t>Diversified Fmcg</t>
+  </si>
+  <si>
+    <t>Coal India Ltd.</t>
+  </si>
+  <si>
+    <t>INE522F01014</t>
+  </si>
+  <si>
+    <t>Consumable Fuels</t>
+  </si>
+  <si>
+    <t>Muthoot Finance Ltd.</t>
+  </si>
+  <si>
+    <t>INE414G01012</t>
+  </si>
+  <si>
+    <t>Finance</t>
+  </si>
+  <si>
+    <t>ICICI Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE090A01021</t>
+  </si>
+  <si>
+    <t>Banks</t>
+  </si>
+  <si>
+    <t>Cummins India Ltd.</t>
+  </si>
+  <si>
+    <t>INE298A01020</t>
+  </si>
+  <si>
+    <t>Industrial Products</t>
+  </si>
+  <si>
+    <t>HDFC Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE040A01034</t>
+  </si>
+  <si>
+    <t>Tata Consultancy Services Ltd.</t>
+  </si>
+  <si>
+    <t>INE467B01029</t>
+  </si>
+  <si>
+    <t>It - Software</t>
+  </si>
+  <si>
+    <t>Bajaj Finance Ltd.</t>
+  </si>
+  <si>
+    <t>INE296A01024</t>
+  </si>
+  <si>
+    <t>PI Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE603J01030</t>
+  </si>
+  <si>
+    <t>Fertilizers &amp; Agrochemicals</t>
+  </si>
+  <si>
+    <t>Torrent Pharmaceuticals Ltd.</t>
+  </si>
+  <si>
+    <t>INE685A01028</t>
+  </si>
+  <si>
+    <t>Pharmaceuticals &amp; Biotechnology</t>
+  </si>
+  <si>
+    <t>Glaxosmithkline Pharmaceuticals Ltd.</t>
+  </si>
+  <si>
+    <t>INE159A01016</t>
+  </si>
+  <si>
+    <t>ICICI Lombard General Insurance Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE765G01017</t>
+  </si>
+  <si>
+    <t>Insurance</t>
+  </si>
+  <si>
+    <t>Eicher Motors Ltd.</t>
+  </si>
+  <si>
+    <t>INE066A01021</t>
+  </si>
+  <si>
+    <t>Automobiles</t>
+  </si>
+  <si>
+    <t>Power Grid Corporation Of India Ltd.</t>
+  </si>
+  <si>
+    <t>INE752E01010</t>
+  </si>
+  <si>
+    <t>Power</t>
+  </si>
+  <si>
+    <t>Oil &amp; Natural Gas Corporation Ltd.</t>
+  </si>
+  <si>
+    <t>INE213A01029</t>
+  </si>
+  <si>
+    <t>Oil</t>
+  </si>
+  <si>
+    <t>Hindustan Unilever Ltd.</t>
+  </si>
+  <si>
+    <t>INE030A01027</t>
+  </si>
+  <si>
+    <t>Petronet LNG Ltd.</t>
+  </si>
+  <si>
+    <t>INE347G01014</t>
+  </si>
+  <si>
+    <t>Gas</t>
+  </si>
+  <si>
+    <t>Lupin Ltd.</t>
+  </si>
+  <si>
+    <t>INE326A01037</t>
+  </si>
+  <si>
+    <t>Abbott India Ltd.</t>
+  </si>
+  <si>
+    <t>INE358A01014</t>
+  </si>
+  <si>
+    <t>Colgate - Palmolive (India) Ltd.</t>
+  </si>
+  <si>
+    <t>INE259A01022</t>
+  </si>
+  <si>
+    <t>Personal Products</t>
+  </si>
+  <si>
     <t>HCL Technologies Ltd.</t>
   </si>
   <si>
     <t>INE860A01027</t>
   </si>
   <si>
-    <t>It - Software</t>
-  </si>
-  <si>
-    <t>Tata Consultancy Services Ltd.</t>
-  </si>
-  <si>
-    <t>INE467B01029</t>
+    <t>Rural Electrification Corporation Ltd.</t>
+  </si>
+  <si>
+    <t>INE020B01018</t>
+  </si>
+  <si>
+    <t>Oil India Ltd.</t>
+  </si>
+  <si>
+    <t>INE274J01014</t>
+  </si>
+  <si>
+    <t>HDFC Asset Management Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE127D01025</t>
+  </si>
+  <si>
+    <t>Capital Markets</t>
+  </si>
+  <si>
+    <t>NMDC Ltd.</t>
+  </si>
+  <si>
+    <t>INE584A01023</t>
+  </si>
+  <si>
+    <t>Minerals &amp; Mining</t>
+  </si>
+  <si>
+    <t>Bharat Petroleum Corporation Ltd.</t>
+  </si>
+  <si>
+    <t>INE029A01011</t>
+  </si>
+  <si>
+    <t>Petroleum Products</t>
+  </si>
+  <si>
+    <t>JSW Steel Ltd.</t>
+  </si>
+  <si>
+    <t>INE019A01038</t>
+  </si>
+  <si>
+    <t>Ferrous Metals</t>
+  </si>
+  <si>
+    <t>LIC Housing Finance Ltd.</t>
+  </si>
+  <si>
+    <t>INE115A01026</t>
+  </si>
+  <si>
+    <t>Kotak Mahindra Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE237A01028</t>
+  </si>
+  <si>
+    <t>Infosys Ltd.</t>
+  </si>
+  <si>
+    <t>INE009A01021</t>
+  </si>
+  <si>
+    <t>Sun Pharmaceutical Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE044A01036</t>
+  </si>
+  <si>
+    <t>Hero Motocorp Ltd.</t>
+  </si>
+  <si>
+    <t>INE158A01026</t>
+  </si>
+  <si>
+    <t>Bajaj Auto Ltd.</t>
+  </si>
+  <si>
+    <t>INE917I01010</t>
+  </si>
+  <si>
+    <t>Mahindra &amp; Mahindra Ltd.</t>
+  </si>
+  <si>
+    <t>INE101A01026</t>
+  </si>
+  <si>
+    <t>Berger Paints India Ltd.</t>
+  </si>
+  <si>
+    <t>INE463A01038</t>
+  </si>
+  <si>
+    <t>Consumer Durables</t>
+  </si>
+  <si>
+    <t>Trent Ltd.</t>
+  </si>
+  <si>
+    <t>INE849A01020</t>
+  </si>
+  <si>
+    <t>Retailing</t>
   </si>
   <si>
     <t>CG Power and Industrial Solutions Ltd.</t>
@@ -85,40 +364,13 @@
     <t>Electrical Equipment</t>
   </si>
   <si>
-    <t>ICICI Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE090A01021</t>
-  </si>
-  <si>
-    <t>Banks</t>
-  </si>
-  <si>
-    <t>Torrent Pharmaceuticals Ltd.</t>
-  </si>
-  <si>
-    <t>INE685A01028</t>
-  </si>
-  <si>
-    <t>Pharmaceuticals &amp; Biotechnology</t>
-  </si>
-  <si>
-    <t>HDFC Asset Management Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE127D01025</t>
-  </si>
-  <si>
-    <t>Capital Markets</t>
-  </si>
-  <si>
-    <t>Bharti Airtel Ltd.</t>
-  </si>
-  <si>
-    <t>INE397D01024</t>
-  </si>
-  <si>
-    <t>Telecom - Services</t>
+    <t>Schaeffler India Ltd.</t>
+  </si>
+  <si>
+    <t>INE513A01022</t>
+  </si>
+  <si>
+    <t>Auto Components</t>
   </si>
   <si>
     <t>Britannia Industries Ltd.</t>
@@ -130,175 +382,22 @@
     <t>Food Products</t>
   </si>
   <si>
-    <t>Cummins India Ltd.</t>
-  </si>
-  <si>
-    <t>INE298A01020</t>
-  </si>
-  <si>
-    <t>Industrial Products</t>
-  </si>
-  <si>
-    <t>Hindustan Unilever Ltd.</t>
-  </si>
-  <si>
-    <t>INE030A01027</t>
-  </si>
-  <si>
-    <t>Diversified Fmcg</t>
-  </si>
-  <si>
-    <t>HDFC Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE040A01034</t>
-  </si>
-  <si>
-    <t>PI Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE603J01030</t>
-  </si>
-  <si>
-    <t>Fertilizers &amp; Agrochemicals</t>
-  </si>
-  <si>
-    <t>Bajaj Finance Ltd.</t>
-  </si>
-  <si>
-    <t>INE296A01024</t>
-  </si>
-  <si>
-    <t>Finance</t>
-  </si>
-  <si>
-    <t>Bajaj Auto Ltd.</t>
-  </si>
-  <si>
-    <t>INE917I01010</t>
-  </si>
-  <si>
-    <t>Automobiles</t>
-  </si>
-  <si>
-    <t>Colgate - Palmolive (India) Ltd.</t>
-  </si>
-  <si>
-    <t>INE259A01022</t>
-  </si>
-  <si>
-    <t>Personal Products</t>
-  </si>
-  <si>
-    <t>Abbott India Ltd.</t>
-  </si>
-  <si>
-    <t>INE358A01014</t>
-  </si>
-  <si>
-    <t>Coal India Ltd.</t>
-  </si>
-  <si>
-    <t>INE522F01014</t>
-  </si>
-  <si>
-    <t>Consumable Fuels</t>
-  </si>
-  <si>
-    <t>Muthoot Finance Ltd.</t>
-  </si>
-  <si>
-    <t>INE414G01012</t>
-  </si>
-  <si>
-    <t>Kotak Mahindra Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE237A01028</t>
-  </si>
-  <si>
-    <t>Infosys Ltd.</t>
-  </si>
-  <si>
-    <t>INE009A01021</t>
-  </si>
-  <si>
-    <t>Power Grid Corporation Of India Ltd.</t>
-  </si>
-  <si>
-    <t>INE752E01010</t>
-  </si>
-  <si>
-    <t>Power</t>
-  </si>
-  <si>
-    <t>Asian Paints Ltd.</t>
-  </si>
-  <si>
-    <t>INE021A01026</t>
-  </si>
-  <si>
-    <t>Consumer Durables</t>
-  </si>
-  <si>
-    <t>Oil India Ltd.</t>
-  </si>
-  <si>
-    <t>INE274J01014</t>
-  </si>
-  <si>
-    <t>Oil</t>
-  </si>
-  <si>
-    <t>Glaxosmithkline Pharmaceuticals Ltd.</t>
-  </si>
-  <si>
-    <t>INE159A01016</t>
-  </si>
-  <si>
-    <t>NMDC Ltd.</t>
-  </si>
-  <si>
-    <t>INE584A01023</t>
-  </si>
-  <si>
-    <t>Minerals &amp; Mining</t>
-  </si>
-  <si>
-    <t>Sun Pharmaceutical Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE044A01036</t>
-  </si>
-  <si>
-    <t>Trent Ltd.</t>
-  </si>
-  <si>
-    <t>INE849A01020</t>
-  </si>
-  <si>
-    <t>Retailing</t>
-  </si>
-  <si>
-    <t>ITC Ltd.</t>
-  </si>
-  <si>
-    <t>INE154A01025</t>
-  </si>
-  <si>
-    <t>Hero Motocorp Ltd.</t>
-  </si>
-  <si>
-    <t>INE158A01026</t>
-  </si>
-  <si>
-    <t>Petronet LNG Ltd.</t>
-  </si>
-  <si>
-    <t>INE347G01014</t>
-  </si>
-  <si>
-    <t>Gas</t>
+    <t>The Indian Hotels Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE053A01029</t>
+  </si>
+  <si>
+    <t>Leisure Services</t>
+  </si>
+  <si>
+    <t>Marico Ltd.</t>
+  </si>
+  <si>
+    <t>INE196A01026</t>
+  </si>
+  <si>
+    <t>Agricultural Food &amp; Other Products</t>
   </si>
   <si>
     <t>SBI Cards &amp; Payment Services Ltd.</t>
@@ -307,28 +406,28 @@
     <t>INE018E01016</t>
   </si>
   <si>
-    <t>Bharat Petroleum Corporation Ltd.</t>
-  </si>
-  <si>
-    <t>INE029A01011</t>
-  </si>
-  <si>
-    <t>Petroleum Products</t>
-  </si>
-  <si>
-    <t>Larsen &amp; Toubro Ltd.</t>
-  </si>
-  <si>
-    <t>INE018A01030</t>
-  </si>
-  <si>
-    <t>Construction</t>
-  </si>
-  <si>
-    <t>IndusInd Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE095A01012</t>
+    <t>Astral Ltd.</t>
+  </si>
+  <si>
+    <t>INE006I01046</t>
+  </si>
+  <si>
+    <t>Indus Towers Ltd.</t>
+  </si>
+  <si>
+    <t>INE121J01017</t>
+  </si>
+  <si>
+    <t>Indian Oil Corporation Ltd.</t>
+  </si>
+  <si>
+    <t>INE242A01010</t>
+  </si>
+  <si>
+    <t>Bandhan Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE545U01014</t>
   </si>
   <si>
     <t>Siemens Ltd.</t>
@@ -337,93 +436,6 @@
     <t>INE003A01024</t>
   </si>
   <si>
-    <t>Hindalco Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE038A01020</t>
-  </si>
-  <si>
-    <t>Non - Ferrous Metals</t>
-  </si>
-  <si>
-    <t>CEAT Ltd.</t>
-  </si>
-  <si>
-    <t>INE482A01020</t>
-  </si>
-  <si>
-    <t>Auto Components</t>
-  </si>
-  <si>
-    <t>The Indian Hotels Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE053A01029</t>
-  </si>
-  <si>
-    <t>Leisure Services</t>
-  </si>
-  <si>
-    <t>Page Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE761H01022</t>
-  </si>
-  <si>
-    <t>Textiles &amp; Apparels</t>
-  </si>
-  <si>
-    <t>Vishal Mega Mart Ltd.</t>
-  </si>
-  <si>
-    <t>INE01EA01019</t>
-  </si>
-  <si>
-    <t>Tata Elxsi Ltd.</t>
-  </si>
-  <si>
-    <t>INE670A01012</t>
-  </si>
-  <si>
-    <t>Dixon Technologies (India) Ltd.</t>
-  </si>
-  <si>
-    <t>INE935N01020</t>
-  </si>
-  <si>
-    <t>Astral Ltd.</t>
-  </si>
-  <si>
-    <t>INE006I01046</t>
-  </si>
-  <si>
-    <t>Eicher Motors Ltd.</t>
-  </si>
-  <si>
-    <t>INE066A01021</t>
-  </si>
-  <si>
-    <t>Bayer Cropscience Ltd.</t>
-  </si>
-  <si>
-    <t>INE462A01022</t>
-  </si>
-  <si>
-    <t>ACC Ltd.</t>
-  </si>
-  <si>
-    <t>INE012A01025</t>
-  </si>
-  <si>
-    <t>Cement &amp; Cement Products</t>
-  </si>
-  <si>
-    <t>Indian Oil Corporation Ltd.</t>
-  </si>
-  <si>
-    <t>INE242A01010</t>
-  </si>
-  <si>
     <t>Container Corporation Of India Ltd.</t>
   </si>
   <si>
@@ -433,40 +445,16 @@
     <t>Transport Services</t>
   </si>
   <si>
-    <t>Bandhan Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE545U01014</t>
-  </si>
-  <si>
-    <t>Schaeffler India Ltd.</t>
-  </si>
-  <si>
-    <t>INE513A01022</t>
-  </si>
-  <si>
-    <t>LIC Housing Finance Ltd.</t>
-  </si>
-  <si>
-    <t>INE115A01026</t>
-  </si>
-  <si>
-    <t>Vedant Fashions Ltd.</t>
-  </si>
-  <si>
-    <t>INE825V01034</t>
-  </si>
-  <si>
-    <t>Grasim Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE047A01021</t>
-  </si>
-  <si>
-    <t>ITC Hotels Ltd</t>
-  </si>
-  <si>
-    <t>INE379A01028</t>
+    <t>SIEMENS ENERGY INDIA LTD</t>
+  </si>
+  <si>
+    <t>INE1NPP01017</t>
+  </si>
+  <si>
+    <t>Tata Communications Ltd.</t>
+  </si>
+  <si>
+    <t>INE151A01013</t>
   </si>
   <si>
     <t>Unlisted</t>
@@ -547,7 +535,7 @@
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -559,7 +547,7 @@
     <t>Benchmark Riskometer</t>
   </si>
   <si>
-    <t>Benchmark name - BSE 200 TRI</t>
+    <t>Benchmark name - S&amp;P BSE 200 TRI</t>
   </si>
 </sst>
 </file>
@@ -930,13 +918,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>118</xdr:row>
+      <xdr:row>116</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>128</xdr:row>
+      <xdr:row>126</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -954,7 +942,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="22936200"/>
+          <a:off x="666750" y="22555200"/>
           <a:ext cx="3590925" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
@@ -969,13 +957,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>133</xdr:row>
+      <xdr:row>131</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>143</xdr:row>
+      <xdr:row>141</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -993,7 +981,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="25793700"/>
+          <a:off x="666750" y="25412700"/>
           <a:ext cx="3590925" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
@@ -1327,14 +1315,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="B1:J132"/>
+  <dimension ref="B1:J130"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="21" width="10.0" collapsed="true"/>
     <col min="2" max="2" bestFit="true" customWidth="true" style="21" width="53.857142857142854" collapsed="true"/>
     <col min="3" max="3" bestFit="true" customWidth="true" style="21" width="16.285714285714285" collapsed="true"/>
     <col min="4" max="4" bestFit="true" customWidth="true" style="21" width="9.714285714285714" collapsed="true"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="21" width="34.142857142857146" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="21" width="36.0" collapsed="true"/>
     <col min="6" max="6" bestFit="true" customWidth="true" style="21" width="10.857142857142858" collapsed="true"/>
     <col min="7" max="7" bestFit="true" customWidth="true" style="21" width="38.714285714285715" collapsed="true"/>
     <col min="8" max="8" bestFit="true" customWidth="true" style="21" width="11.714285714285714" collapsed="true"/>
@@ -1427,10 +1415,10 @@
         <v>13</v>
       </c>
       <c r="G5" s="9">
-        <v>10290.649999999998</v>
+        <v>12189.899999999998</v>
       </c>
       <c r="H5" s="10">
-        <v>0.8804543423112002</v>
+        <v>0.9217379231337999</v>
       </c>
       <c r="I5" s="9" t="s">
         <v>13</v>
@@ -1464,10 +1452,10 @@
         <v>13</v>
       </c>
       <c r="G7" s="9">
-        <v>10290.649999999998</v>
+        <v>12189.899999999998</v>
       </c>
       <c r="H7" s="10">
-        <v>0.8804543423112002</v>
+        <v>0.9217379231337999</v>
       </c>
       <c r="I7" s="9" t="s">
         <v>13</v>
@@ -1490,13 +1478,13 @@
         <v>17</v>
       </c>
       <c r="F8" s="14">
-        <v>33662</v>
+        <v>42563</v>
       </c>
       <c r="G8" s="15">
-        <v>580.82</v>
+        <v>801.38</v>
       </c>
       <c r="H8" s="16">
-        <v>0.0496941875491</v>
+        <v>0.0605962589392</v>
       </c>
       <c r="I8" s="15" t="s">
         <v>13</v>
@@ -1516,16 +1504,16 @@
         <v>13</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F9" s="14">
-        <v>9500</v>
+        <v>37236</v>
       </c>
       <c r="G9" s="15">
-        <v>390.68</v>
+        <v>691.17</v>
       </c>
       <c r="H9" s="16">
-        <v>0.0334260617604</v>
+        <v>0.0522627421335</v>
       </c>
       <c r="I9" s="15" t="s">
         <v>13</v>
@@ -1536,25 +1524,25 @@
     </row>
     <row r="10" spans="2:10" ht="15" customHeight="1">
       <c r="B10" s="12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D10" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F10" s="14">
-        <v>56531</v>
+        <v>120402</v>
       </c>
       <c r="G10" s="15">
-        <v>358.89</v>
+        <v>503.34</v>
       </c>
       <c r="H10" s="16">
-        <v>0.0307061515951</v>
+        <v>0.038059997722</v>
       </c>
       <c r="I10" s="15" t="s">
         <v>13</v>
@@ -1565,25 +1553,25 @@
     </row>
     <row r="11" spans="2:10" ht="15" customHeight="1">
       <c r="B11" s="12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D11" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F11" s="14">
-        <v>27291</v>
+        <v>113250</v>
       </c>
       <c r="G11" s="15">
-        <v>341.90</v>
+        <v>449.94</v>
       </c>
       <c r="H11" s="16">
-        <v>0.0292525097673</v>
+        <v>0.0340221627032</v>
       </c>
       <c r="I11" s="15" t="s">
         <v>13</v>
@@ -1594,25 +1582,25 @@
     </row>
     <row r="12" spans="2:10" ht="15" customHeight="1">
       <c r="B12" s="12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D12" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F12" s="14">
-        <v>10048</v>
+        <v>18317</v>
       </c>
       <c r="G12" s="15">
-        <v>328.48</v>
+        <v>405.79</v>
       </c>
       <c r="H12" s="16">
-        <v>0.0281043123965</v>
+        <v>0.0306837653983</v>
       </c>
       <c r="I12" s="15" t="s">
         <v>13</v>
@@ -1623,25 +1611,25 @@
     </row>
     <row r="13" spans="2:10" ht="15" customHeight="1">
       <c r="B13" s="12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D13" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F13" s="14">
-        <v>8086</v>
+        <v>27291</v>
       </c>
       <c r="G13" s="15">
-        <v>312.92</v>
+        <v>394.57</v>
       </c>
       <c r="H13" s="16">
-        <v>0.0267730194688</v>
+        <v>0.029835366355</v>
       </c>
       <c r="I13" s="15" t="s">
         <v>13</v>
@@ -1652,25 +1640,25 @@
     </row>
     <row r="14" spans="2:10" ht="15" customHeight="1">
       <c r="B14" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F14" s="14">
-        <v>19037</v>
+        <v>10320</v>
       </c>
       <c r="G14" s="15">
-        <v>309.6</v>
+        <v>337.27</v>
       </c>
       <c r="H14" s="16">
-        <v>0.0264889646796</v>
+        <v>0.0255026332731</v>
       </c>
       <c r="I14" s="15" t="s">
         <v>13</v>
@@ -1681,25 +1669,25 @@
     </row>
     <row r="15" spans="2:10" ht="15" customHeight="1">
       <c r="B15" s="12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F15" s="14">
-        <v>5937</v>
+        <v>17262</v>
       </c>
       <c r="G15" s="15">
-        <v>304.55</v>
+        <v>335.73</v>
       </c>
       <c r="H15" s="16">
-        <v>0.0260568933888</v>
+        <v>0.0253861863456</v>
       </c>
       <c r="I15" s="15" t="s">
         <v>13</v>
@@ -1722,13 +1710,13 @@
         <v>40</v>
       </c>
       <c r="F16" s="14">
-        <v>10320</v>
+        <v>9500</v>
       </c>
       <c r="G16" s="15">
-        <v>300.73</v>
+        <v>329.02</v>
       </c>
       <c r="H16" s="16">
-        <v>0.0257300592638</v>
+        <v>0.0248788104472</v>
       </c>
       <c r="I16" s="15" t="s">
         <v>13</v>
@@ -1748,16 +1736,16 @@
         <v>13</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="F17" s="14">
-        <v>12100</v>
+        <v>3514</v>
       </c>
       <c r="G17" s="15">
-        <v>298.72</v>
+        <v>322.6</v>
       </c>
       <c r="H17" s="16">
-        <v>0.0255580863342</v>
+        <v>0.0243933628662</v>
       </c>
       <c r="I17" s="15" t="s">
         <v>13</v>
@@ -1768,25 +1756,25 @@
     </row>
     <row r="18" spans="2:10" ht="15" customHeight="1">
       <c r="B18" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="C18" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="C18" s="13" t="s">
+      <c r="D18" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="D18" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>25</v>
-      </c>
       <c r="F18" s="14">
-        <v>17262</v>
+        <v>8398</v>
       </c>
       <c r="G18" s="15">
-        <v>293.24</v>
+        <v>321.11</v>
       </c>
       <c r="H18" s="16">
-        <v>0.0250892248147</v>
+        <v>0.0242806966831</v>
       </c>
       <c r="I18" s="15" t="s">
         <v>13</v>
@@ -1809,13 +1797,13 @@
         <v>48</v>
       </c>
       <c r="F19" s="14">
-        <v>8398</v>
+        <v>10048</v>
       </c>
       <c r="G19" s="15">
-        <v>292.57</v>
+        <v>318.99</v>
       </c>
       <c r="H19" s="16">
-        <v>0.0250319005048</v>
+        <v>0.0241203931206</v>
       </c>
       <c r="I19" s="15" t="s">
         <v>13</v>
@@ -1835,16 +1823,16 @@
         <v>13</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F20" s="14">
-        <v>3514</v>
+        <v>9572</v>
       </c>
       <c r="G20" s="15">
-        <v>277.08</v>
+        <v>315.74</v>
       </c>
       <c r="H20" s="16">
-        <v>0.0237065966842</v>
+        <v>0.0238746447346</v>
       </c>
       <c r="I20" s="15" t="s">
         <v>13</v>
@@ -1855,25 +1843,25 @@
     </row>
     <row r="21" spans="2:10" ht="15" customHeight="1">
       <c r="B21" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C21" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="C21" s="13" t="s">
+      <c r="D21" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="D21" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E21" s="13" t="s">
-        <v>54</v>
-      </c>
       <c r="F21" s="14">
-        <v>2984</v>
+        <v>16171</v>
       </c>
       <c r="G21" s="15">
-        <v>264.02</v>
+        <v>303.27</v>
       </c>
       <c r="H21" s="16">
-        <v>0.0225892004351</v>
+        <v>0.0229317270814</v>
       </c>
       <c r="I21" s="15" t="s">
         <v>13</v>
@@ -1884,25 +1872,25 @@
     </row>
     <row r="22" spans="2:10" ht="15" customHeight="1">
       <c r="B22" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="C22" s="13" t="s">
+      <c r="D22" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E22" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>57</v>
-      </c>
       <c r="F22" s="14">
-        <v>9318</v>
+        <v>5608</v>
       </c>
       <c r="G22" s="15">
-        <v>262.91</v>
+        <v>299.1</v>
       </c>
       <c r="H22" s="16">
-        <v>0.0224942303098</v>
+        <v>0.0226164129984</v>
       </c>
       <c r="I22" s="15" t="s">
         <v>13</v>
@@ -1913,25 +1901,25 @@
     </row>
     <row r="23" spans="2:10" ht="15" customHeight="1">
       <c r="B23" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="C23" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="C23" s="13" t="s">
+      <c r="D23" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E23" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="D23" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>28</v>
-      </c>
       <c r="F23" s="14">
-        <v>972</v>
+        <v>102819</v>
       </c>
       <c r="G23" s="15">
-        <v>254.40</v>
+        <v>297.92</v>
       </c>
       <c r="H23" s="16">
-        <v>0.0217661260158</v>
+        <v>0.0225271874306</v>
       </c>
       <c r="I23" s="15" t="s">
         <v>13</v>
@@ -1954,13 +1942,13 @@
         <v>62</v>
       </c>
       <c r="F24" s="14">
-        <v>62483</v>
+        <v>119243</v>
       </c>
       <c r="G24" s="15">
-        <v>247.37</v>
+        <v>285.47</v>
       </c>
       <c r="H24" s="16">
-        <v>0.0211646485555</v>
+        <v>0.0215857820751</v>
       </c>
       <c r="I24" s="15" t="s">
         <v>13</v>
@@ -1980,16 +1968,16 @@
         <v>13</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="F25" s="14">
-        <v>10658</v>
+        <v>12100</v>
       </c>
       <c r="G25" s="15">
-        <v>240.74</v>
+        <v>284.14</v>
       </c>
       <c r="H25" s="16">
-        <v>0.0205973945638</v>
+        <v>0.0214852142741</v>
       </c>
       <c r="I25" s="15" t="s">
         <v>13</v>
@@ -2009,16 +1997,16 @@
         <v>13</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>25</v>
+        <v>67</v>
       </c>
       <c r="F26" s="14">
-        <v>12611</v>
+        <v>82426</v>
       </c>
       <c r="G26" s="15">
-        <v>239.77</v>
+        <v>253.30</v>
       </c>
       <c r="H26" s="16">
-        <v>0.0205144026525</v>
+        <v>0.0191532511284</v>
       </c>
       <c r="I26" s="15" t="s">
         <v>13</v>
@@ -2029,25 +2017,25 @@
     </row>
     <row r="27" spans="2:10" ht="15" customHeight="1">
       <c r="B27" s="12" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="F27" s="14">
-        <v>12304</v>
+        <v>12506</v>
       </c>
       <c r="G27" s="15">
-        <v>231.29</v>
+        <v>244.83</v>
       </c>
       <c r="H27" s="16">
-        <v>0.0197888651186</v>
+        <v>0.0185127930271</v>
       </c>
       <c r="I27" s="15" t="s">
         <v>13</v>
@@ -2058,25 +2046,25 @@
     </row>
     <row r="28" spans="2:10" ht="15" customHeight="1">
       <c r="B28" s="12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="F28" s="14">
-        <v>75879</v>
+        <v>769</v>
       </c>
       <c r="G28" s="15">
-        <v>228.89</v>
+        <v>234.20</v>
       </c>
       <c r="H28" s="16">
-        <v>0.0195835243072</v>
+        <v>0.0177090067677</v>
       </c>
       <c r="I28" s="15" t="s">
         <v>13</v>
@@ -2099,13 +2087,13 @@
         <v>74</v>
       </c>
       <c r="F29" s="14">
-        <v>9658</v>
+        <v>9318</v>
       </c>
       <c r="G29" s="15">
-        <v>222.21</v>
+        <v>228.84</v>
       </c>
       <c r="H29" s="16">
-        <v>0.0190119923819</v>
+        <v>0.0173037109681</v>
       </c>
       <c r="I29" s="15" t="s">
         <v>13</v>
@@ -2125,16 +2113,16 @@
         <v>13</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>77</v>
+        <v>40</v>
       </c>
       <c r="F30" s="14">
-        <v>51291</v>
+        <v>13955</v>
       </c>
       <c r="G30" s="15">
-        <v>215.65</v>
+        <v>228.39</v>
       </c>
       <c r="H30" s="16">
-        <v>0.0184507274972</v>
+        <v>0.0172696842685</v>
       </c>
       <c r="I30" s="15" t="s">
         <v>13</v>
@@ -2145,25 +2133,25 @@
     </row>
     <row r="31" spans="2:10" ht="15" customHeight="1">
       <c r="B31" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="C31" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>79</v>
-      </c>
       <c r="D31" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F31" s="14">
-        <v>10650</v>
+        <v>55961</v>
       </c>
       <c r="G31" s="15">
-        <v>210.57</v>
+        <v>225.13</v>
       </c>
       <c r="H31" s="16">
-        <v>0.0180160894463</v>
+        <v>0.0170231797336</v>
       </c>
       <c r="I31" s="15" t="s">
         <v>13</v>
@@ -2174,25 +2162,25 @@
     </row>
     <row r="32" spans="2:10" ht="15" customHeight="1">
       <c r="B32" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="C32" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="C32" s="13" t="s">
-        <v>81</v>
-      </c>
       <c r="D32" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="F32" s="14">
-        <v>297597</v>
+        <v>51291</v>
       </c>
       <c r="G32" s="15">
-        <v>196.71</v>
+        <v>218.91</v>
       </c>
       <c r="H32" s="16">
-        <v>0.0168302462601</v>
+        <v>0.0165528551303</v>
       </c>
       <c r="I32" s="15" t="s">
         <v>13</v>
@@ -2203,25 +2191,25 @@
     </row>
     <row r="33" spans="2:10" ht="15" customHeight="1">
       <c r="B33" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="C33" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="D33" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E33" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="C33" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="D33" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>28</v>
-      </c>
       <c r="F33" s="14">
-        <v>11019</v>
+        <v>4538</v>
       </c>
       <c r="G33" s="15">
-        <v>192.17</v>
+        <v>217.05</v>
       </c>
       <c r="H33" s="16">
-        <v>0.0164418098917</v>
+        <v>0.0164122114387</v>
       </c>
       <c r="I33" s="15" t="s">
         <v>13</v>
@@ -2232,25 +2220,25 @@
     </row>
     <row r="34" spans="2:10" ht="15" customHeight="1">
       <c r="B34" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="C34" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="C34" s="13" t="s">
+      <c r="D34" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E34" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="D34" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E34" s="13" t="s">
-        <v>87</v>
-      </c>
       <c r="F34" s="14">
-        <v>3161</v>
+        <v>297597</v>
       </c>
       <c r="G34" s="15">
-        <v>181.86</v>
+        <v>211.80</v>
       </c>
       <c r="H34" s="16">
-        <v>0.0155596999891</v>
+        <v>0.0160152332767</v>
       </c>
       <c r="I34" s="15" t="s">
         <v>13</v>
@@ -2261,25 +2249,25 @@
     </row>
     <row r="35" spans="2:10" ht="15" customHeight="1">
       <c r="B35" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="C35" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="C35" s="13" t="s">
+      <c r="D35" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E35" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="D35" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E35" s="13" t="s">
-        <v>43</v>
-      </c>
       <c r="F35" s="14">
-        <v>39090</v>
+        <v>61821</v>
       </c>
       <c r="G35" s="15">
-        <v>174.93</v>
+        <v>196.84</v>
       </c>
       <c r="H35" s="16">
-        <v>0.014966778396</v>
+        <v>0.0148840345523</v>
       </c>
       <c r="I35" s="15" t="s">
         <v>13</v>
@@ -2299,16 +2287,16 @@
         <v>13</v>
       </c>
       <c r="E36" s="13" t="s">
-        <v>54</v>
+        <v>92</v>
       </c>
       <c r="F36" s="14">
-        <v>4006</v>
+        <v>19700</v>
       </c>
       <c r="G36" s="15">
-        <v>173.83</v>
+        <v>195.72</v>
       </c>
       <c r="H36" s="16">
-        <v>0.0148726638574</v>
+        <v>0.0147993458778</v>
       </c>
       <c r="I36" s="15" t="s">
         <v>13</v>
@@ -2319,25 +2307,25 @@
     </row>
     <row r="37" spans="2:10" ht="15" customHeight="1">
       <c r="B37" s="12" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D37" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>94</v>
+        <v>29</v>
       </c>
       <c r="F37" s="14">
-        <v>54632</v>
+        <v>32477</v>
       </c>
       <c r="G37" s="15">
-        <v>172.75</v>
+        <v>193.71</v>
       </c>
       <c r="H37" s="16">
-        <v>0.0147802604922</v>
+        <v>0.0146473599529</v>
       </c>
       <c r="I37" s="15" t="s">
         <v>13</v>
@@ -2357,16 +2345,16 @@
         <v>13</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="F38" s="14">
-        <v>20759</v>
+        <v>9272</v>
       </c>
       <c r="G38" s="15">
-        <v>161.55</v>
+        <v>192.37</v>
       </c>
       <c r="H38" s="16">
-        <v>0.013822003372</v>
+        <v>0.014546036003</v>
       </c>
       <c r="I38" s="15" t="s">
         <v>13</v>
@@ -2386,16 +2374,16 @@
         <v>13</v>
       </c>
       <c r="E39" s="13" t="s">
-        <v>99</v>
+        <v>40</v>
       </c>
       <c r="F39" s="14">
-        <v>61821</v>
+        <v>12304</v>
       </c>
       <c r="G39" s="15">
-        <v>161.41</v>
+        <v>192.27</v>
       </c>
       <c r="H39" s="16">
-        <v>0.013810025158</v>
+        <v>0.0145384745142</v>
       </c>
       <c r="I39" s="15" t="s">
         <v>13</v>
@@ -2406,25 +2394,25 @@
     </row>
     <row r="40" spans="2:10" ht="15" customHeight="1">
       <c r="B40" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="C40" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="C40" s="13" t="s">
-        <v>101</v>
-      </c>
       <c r="D40" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>102</v>
+        <v>48</v>
       </c>
       <c r="F40" s="14">
-        <v>4047</v>
+        <v>11019</v>
       </c>
       <c r="G40" s="15">
-        <v>144.37</v>
+        <v>184.85</v>
       </c>
       <c r="H40" s="16">
-        <v>0.0123521053966</v>
+        <v>0.0139774120453</v>
       </c>
       <c r="I40" s="15" t="s">
         <v>13</v>
@@ -2435,25 +2423,25 @@
     </row>
     <row r="41" spans="2:10" ht="15" customHeight="1">
       <c r="B41" s="12" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D41" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E41" s="13" t="s">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="F41" s="14">
-        <v>13857</v>
+        <v>4006</v>
       </c>
       <c r="G41" s="15">
-        <v>137.35</v>
+        <v>172.63</v>
       </c>
       <c r="H41" s="16">
-        <v>0.011751483523</v>
+        <v>0.0130533981141</v>
       </c>
       <c r="I41" s="15" t="s">
         <v>13</v>
@@ -2464,25 +2452,25 @@
     </row>
     <row r="42" spans="2:10" ht="15" customHeight="1">
       <c r="B42" s="12" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D42" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E42" s="13" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="F42" s="14">
-        <v>2173</v>
+        <v>1880</v>
       </c>
       <c r="G42" s="15">
-        <v>131.97</v>
+        <v>161.81</v>
       </c>
       <c r="H42" s="16">
-        <v>0.0112911778707</v>
+        <v>0.012235245026</v>
       </c>
       <c r="I42" s="15" t="s">
         <v>13</v>
@@ -2493,25 +2481,25 @@
     </row>
     <row r="43" spans="2:10" ht="15" customHeight="1">
       <c r="B43" s="12" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D43" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>109</v>
+        <v>56</v>
       </c>
       <c r="F43" s="14">
-        <v>21610</v>
+        <v>5131</v>
       </c>
       <c r="G43" s="15">
-        <v>128.43</v>
+        <v>152.74</v>
       </c>
       <c r="H43" s="16">
-        <v>0.0109883001737</v>
+        <v>0.0115494179919</v>
       </c>
       <c r="I43" s="15" t="s">
         <v>13</v>
@@ -2522,25 +2510,25 @@
     </row>
     <row r="44" spans="2:10" ht="15" customHeight="1">
       <c r="B44" s="12" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D44" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="F44" s="14">
-        <v>4042</v>
+        <v>24268</v>
       </c>
       <c r="G44" s="15">
-        <v>115.47</v>
+        <v>137.92</v>
       </c>
       <c r="H44" s="16">
-        <v>0.0098794597918</v>
+        <v>0.0104288053518</v>
       </c>
       <c r="I44" s="15" t="s">
         <v>13</v>
@@ -2551,25 +2539,25 @@
     </row>
     <row r="45" spans="2:10" ht="15" customHeight="1">
       <c r="B45" s="12" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D45" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="F45" s="14">
-        <v>14832</v>
+        <v>2412</v>
       </c>
       <c r="G45" s="15">
-        <v>113.42</v>
+        <v>136.12</v>
       </c>
       <c r="H45" s="16">
-        <v>0.0097040645153</v>
+        <v>0.0102926985535</v>
       </c>
       <c r="I45" s="15" t="s">
         <v>13</v>
@@ -2580,25 +2568,25 @@
     </row>
     <row r="46" spans="2:10" ht="15" customHeight="1">
       <c r="B46" s="12" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C46" s="13" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D46" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F46" s="14">
-        <v>244</v>
+        <v>17373</v>
       </c>
       <c r="G46" s="15">
-        <v>109.13</v>
+        <v>119.30</v>
       </c>
       <c r="H46" s="16">
-        <v>0.0093370178148</v>
+        <v>0.0090208561374</v>
       </c>
       <c r="I46" s="15" t="s">
         <v>13</v>
@@ -2609,25 +2597,25 @@
     </row>
     <row r="47" spans="2:10" ht="15" customHeight="1">
       <c r="B47" s="12" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D47" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E47" s="13" t="s">
-        <v>87</v>
+        <v>118</v>
       </c>
       <c r="F47" s="14">
-        <v>96140</v>
+        <v>2715</v>
       </c>
       <c r="G47" s="15">
-        <v>103.78</v>
+        <v>113.72</v>
       </c>
       <c r="H47" s="16">
-        <v>0.0088792789226</v>
+        <v>0.0085989250624</v>
       </c>
       <c r="I47" s="15" t="s">
         <v>13</v>
@@ -2638,25 +2626,25 @@
     </row>
     <row r="48" spans="2:10" ht="15" customHeight="1">
       <c r="B48" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="C48" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="D48" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E48" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="C48" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="D48" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E48" s="13" t="s">
-        <v>17</v>
-      </c>
       <c r="F48" s="14">
-        <v>1470</v>
+        <v>2060</v>
       </c>
       <c r="G48" s="15">
-        <v>93.14</v>
+        <v>113.52</v>
       </c>
       <c r="H48" s="16">
-        <v>0.0079689346584</v>
+        <v>0.0085838020848</v>
       </c>
       <c r="I48" s="15" t="s">
         <v>13</v>
@@ -2667,25 +2655,25 @@
     </row>
     <row r="49" spans="2:10" ht="15" customHeight="1">
       <c r="B49" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="C49" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="C49" s="13" t="s">
+      <c r="D49" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E49" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="D49" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E49" s="13" t="s">
-        <v>74</v>
-      </c>
       <c r="F49" s="14">
-        <v>602</v>
+        <v>14030</v>
       </c>
       <c r="G49" s="15">
-        <v>90.22</v>
+        <v>108.01</v>
       </c>
       <c r="H49" s="16">
-        <v>0.0077191033378</v>
+        <v>0.008167164052</v>
       </c>
       <c r="I49" s="15" t="s">
         <v>13</v>
@@ -2705,16 +2693,16 @@
         <v>13</v>
       </c>
       <c r="E50" s="13" t="s">
-        <v>40</v>
+        <v>127</v>
       </c>
       <c r="F50" s="14">
-        <v>5956</v>
+        <v>14982</v>
       </c>
       <c r="G50" s="15">
-        <v>89.77</v>
+        <v>107.34</v>
       </c>
       <c r="H50" s="16">
-        <v>0.0076806019356</v>
+        <v>0.008116502077</v>
       </c>
       <c r="I50" s="15" t="s">
         <v>13</v>
@@ -2725,25 +2713,25 @@
     </row>
     <row r="51" spans="2:10" ht="15" customHeight="1">
       <c r="B51" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C51" s="13" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D51" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E51" s="13" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="F51" s="14">
-        <v>1620</v>
+        <v>10493</v>
       </c>
       <c r="G51" s="15">
-        <v>84.15</v>
+        <v>96.65</v>
       </c>
       <c r="H51" s="16">
-        <v>0.0071997622021</v>
+        <v>0.0073081789244</v>
       </c>
       <c r="I51" s="15" t="s">
         <v>13</v>
@@ -2754,25 +2742,25 @@
     </row>
     <row r="52" spans="2:10" ht="15" customHeight="1">
       <c r="B52" s="12" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D52" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E52" s="13" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="F52" s="14">
-        <v>1632</v>
+        <v>5956</v>
       </c>
       <c r="G52" s="15">
-        <v>83.49</v>
+        <v>89.23</v>
       </c>
       <c r="H52" s="16">
-        <v>0.007143293479</v>
+        <v>0.0067471164555</v>
       </c>
       <c r="I52" s="15" t="s">
         <v>13</v>
@@ -2783,25 +2771,25 @@
     </row>
     <row r="53" spans="2:10" ht="15" customHeight="1">
       <c r="B53" s="12" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C53" s="13" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D53" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E53" s="13" t="s">
-        <v>133</v>
+        <v>20</v>
       </c>
       <c r="F53" s="14">
-        <v>4102</v>
+        <v>20284</v>
       </c>
       <c r="G53" s="15">
-        <v>82.35</v>
+        <v>77.92</v>
       </c>
       <c r="H53" s="16">
-        <v>0.0070457565935</v>
+        <v>0.0058919120723</v>
       </c>
       <c r="I53" s="15" t="s">
         <v>13</v>
@@ -2821,16 +2809,16 @@
         <v>13</v>
       </c>
       <c r="E54" s="13" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="F54" s="14">
         <v>54369</v>
       </c>
       <c r="G54" s="15">
-        <v>69.86</v>
+        <v>77.19</v>
       </c>
       <c r="H54" s="16">
-        <v>0.0059771287872</v>
+        <v>0.0058367132041</v>
       </c>
       <c r="I54" s="15" t="s">
         <v>13</v>
@@ -2850,16 +2838,16 @@
         <v>13</v>
       </c>
       <c r="E55" s="13" t="s">
-        <v>138</v>
+        <v>32</v>
       </c>
       <c r="F55" s="14">
-        <v>8733</v>
+        <v>44605</v>
       </c>
       <c r="G55" s="15">
-        <v>68.13</v>
+        <v>75.91</v>
       </c>
       <c r="H55" s="16">
-        <v>0.0058291122856</v>
+        <v>0.0057399261474</v>
       </c>
       <c r="I55" s="15" t="s">
         <v>13</v>
@@ -2870,25 +2858,25 @@
     </row>
     <row r="56" spans="2:10" ht="15" customHeight="1">
       <c r="B56" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="C56" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="C56" s="13" t="s">
-        <v>140</v>
-      </c>
       <c r="D56" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E56" s="13" t="s">
-        <v>25</v>
+        <v>115</v>
       </c>
       <c r="F56" s="14">
-        <v>44605</v>
+        <v>2173</v>
       </c>
       <c r="G56" s="15">
-        <v>67.52</v>
+        <v>70.96</v>
       </c>
       <c r="H56" s="16">
-        <v>0.005776921496</v>
+        <v>0.0053656324519</v>
       </c>
       <c r="I56" s="15" t="s">
         <v>13</v>
@@ -2899,25 +2887,25 @@
     </row>
     <row r="57" spans="2:10" ht="15" customHeight="1">
       <c r="B57" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="C57" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="C57" s="13" t="s">
+      <c r="D57" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E57" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="D57" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E57" s="13" t="s">
-        <v>112</v>
-      </c>
       <c r="F57" s="14">
-        <v>1560</v>
+        <v>8733</v>
       </c>
       <c r="G57" s="15">
-        <v>53.44</v>
+        <v>68.50</v>
       </c>
       <c r="H57" s="16">
-        <v>0.004572255402</v>
+        <v>0.0051796198274</v>
       </c>
       <c r="I57" s="15" t="s">
         <v>13</v>
@@ -2937,16 +2925,16 @@
         <v>13</v>
       </c>
       <c r="E58" s="13" t="s">
-        <v>51</v>
+        <v>115</v>
       </c>
       <c r="F58" s="14">
-        <v>8146</v>
+        <v>2173</v>
       </c>
       <c r="G58" s="15">
-        <v>48.72</v>
+        <v>53.85</v>
       </c>
       <c r="H58" s="16">
-        <v>0.0041684184728</v>
+        <v>0.0040718617183</v>
       </c>
       <c r="I58" s="15" t="s">
         <v>13</v>
@@ -2966,16 +2954,16 @@
         <v>13</v>
       </c>
       <c r="E59" s="13" t="s">
-        <v>87</v>
+        <v>20</v>
       </c>
       <c r="F59" s="14">
-        <v>4859</v>
+        <v>2495</v>
       </c>
       <c r="G59" s="15">
-        <v>45.37</v>
+        <v>41.82</v>
       </c>
       <c r="H59" s="16">
-        <v>0.0038817969234</v>
+        <v>0.0031622146158</v>
       </c>
       <c r="I59" s="15" t="s">
         <v>13</v>
@@ -2986,56 +2974,35 @@
     </row>
     <row r="60" spans="2:10" ht="15" customHeight="1">
       <c r="B60" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J60" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="61" spans="2:10" ht="15" customHeight="1">
+      <c r="B61" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="C60" s="13" t="s">
+      <c r="C61" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D61" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E61" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F61" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G61" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="D60" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E60" s="13" t="s">
-        <v>133</v>
-      </c>
-      <c r="F60" s="14">
-        <v>235</v>
-      </c>
-      <c r="G60" s="15">
-        <v>5.90</v>
-      </c>
-      <c r="H60" s="16">
-        <v>0.0005047961615</v>
-      </c>
-      <c r="I60" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J60" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="61" spans="2:10" ht="15" customHeight="1">
-      <c r="B61" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="C61" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="D61" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E61" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="F61" s="14">
-        <v>898</v>
-      </c>
-      <c r="G61" s="15">
-        <v>1.46</v>
-      </c>
-      <c r="H61" s="16">
-        <v>0.0001249156603</v>
-      </c>
-      <c r="I61" s="15" t="s">
+      <c r="H61" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="I61" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J61" s="11" t="s">
@@ -3052,7 +3019,7 @@
     </row>
     <row r="63" spans="2:10" ht="15" customHeight="1">
       <c r="B63" s="7" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C63" s="8" t="s">
         <v>13</v>
@@ -3067,10 +3034,10 @@
         <v>13</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="I63" s="9" t="s">
         <v>13</v>
@@ -3089,7 +3056,7 @@
     </row>
     <row r="65" spans="2:10" ht="15" customHeight="1">
       <c r="B65" s="7" t="s">
-        <v>153</v>
+        <v>14</v>
       </c>
       <c r="C65" s="8" t="s">
         <v>13</v>
@@ -3104,10 +3071,10 @@
         <v>13</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="I65" s="9" t="s">
         <v>13</v>
@@ -3126,7 +3093,7 @@
     </row>
     <row r="67" spans="2:10" ht="15" customHeight="1">
       <c r="B67" s="7" t="s">
-        <v>14</v>
+        <v>150</v>
       </c>
       <c r="C67" s="8" t="s">
         <v>13</v>
@@ -3141,10 +3108,10 @@
         <v>13</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="I67" s="9" t="s">
         <v>13</v>
@@ -3163,7 +3130,7 @@
     </row>
     <row r="69" spans="2:10" ht="15" customHeight="1">
       <c r="B69" s="7" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C69" s="8" t="s">
         <v>13</v>
@@ -3178,10 +3145,10 @@
         <v>13</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="I69" s="9" t="s">
         <v>13</v>
@@ -3200,7 +3167,7 @@
     </row>
     <row r="71" spans="2:10" ht="15" customHeight="1">
       <c r="B71" s="7" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C71" s="8" t="s">
         <v>13</v>
@@ -3215,10 +3182,10 @@
         <v>13</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="I71" s="9" t="s">
         <v>13</v>
@@ -3237,7 +3204,7 @@
     </row>
     <row r="73" spans="2:10" ht="15" customHeight="1">
       <c r="B73" s="7" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C73" s="8" t="s">
         <v>13</v>
@@ -3252,10 +3219,10 @@
         <v>13</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="I73" s="9" t="s">
         <v>13</v>
@@ -3274,7 +3241,7 @@
     </row>
     <row r="75" spans="2:10" ht="15" customHeight="1">
       <c r="B75" s="7" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C75" s="8" t="s">
         <v>13</v>
@@ -3289,10 +3256,10 @@
         <v>13</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="I75" s="9" t="s">
         <v>13</v>
@@ -3311,7 +3278,7 @@
     </row>
     <row r="77" spans="2:10" ht="15" customHeight="1">
       <c r="B77" s="7" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C77" s="8" t="s">
         <v>13</v>
@@ -3326,10 +3293,10 @@
         <v>13</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="I77" s="9" t="s">
         <v>13</v>
@@ -3348,7 +3315,7 @@
     </row>
     <row r="79" spans="2:10" ht="15" customHeight="1">
       <c r="B79" s="7" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C79" s="8" t="s">
         <v>13</v>
@@ -3363,10 +3330,10 @@
         <v>13</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="I79" s="9" t="s">
         <v>13</v>
@@ -3385,7 +3352,7 @@
     </row>
     <row r="81" spans="2:10" ht="15" customHeight="1">
       <c r="B81" s="7" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C81" s="8" t="s">
         <v>13</v>
@@ -3400,10 +3367,10 @@
         <v>13</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="I81" s="9" t="s">
         <v>13</v>
@@ -3422,7 +3389,7 @@
     </row>
     <row r="83" spans="2:10" ht="15" customHeight="1">
       <c r="B83" s="7" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C83" s="8" t="s">
         <v>13</v>
@@ -3437,10 +3404,10 @@
         <v>13</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="H83" s="10" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="I83" s="9" t="s">
         <v>13</v>
@@ -3459,7 +3426,7 @@
     </row>
     <row r="85" spans="2:10" ht="15" customHeight="1">
       <c r="B85" s="7" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C85" s="8" t="s">
         <v>13</v>
@@ -3474,10 +3441,10 @@
         <v>13</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="H85" s="10" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="I85" s="9" t="s">
         <v>13</v>
@@ -3496,7 +3463,7 @@
     </row>
     <row r="87" spans="2:10" ht="15" customHeight="1">
       <c r="B87" s="7" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C87" s="8" t="s">
         <v>13</v>
@@ -3510,11 +3477,11 @@
       <c r="F87" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G87" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="H87" s="10" t="s">
-        <v>152</v>
+      <c r="G87" s="9">
+        <v>687.74</v>
+      </c>
+      <c r="H87" s="10">
+        <v>0.0520033830677</v>
       </c>
       <c r="I87" s="9" t="s">
         <v>13</v>
@@ -3533,7 +3500,7 @@
     </row>
     <row r="89" spans="2:10" ht="15" customHeight="1">
       <c r="B89" s="7" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C89" s="8" t="s">
         <v>13</v>
@@ -3548,10 +3515,10 @@
         <v>13</v>
       </c>
       <c r="G89" s="9">
-        <v>1039.4</v>
+        <v>349.9999944</v>
       </c>
       <c r="H89" s="10">
-        <v>0.0889296831007</v>
+        <v>0.0264652103738</v>
       </c>
       <c r="I89" s="9" t="s">
         <v>13</v>
@@ -3562,6 +3529,20 @@
     </row>
     <row r="90" spans="2:10" ht="15" customHeight="1">
       <c r="B90" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="C90" s="13"/>
+      <c r="D90" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E90" s="13"/>
+      <c r="G90" s="15">
+        <v>349.9999944</v>
+      </c>
+      <c r="H90" s="16">
+        <v>0.0264652103738</v>
+      </c>
+      <c r="I90" s="15" t="s">
         <v>13</v>
       </c>
       <c r="J90" s="11" t="s">
@@ -3569,233 +3550,205 @@
       </c>
     </row>
     <row r="91" spans="2:10" ht="15" customHeight="1">
-      <c r="B91" s="7" t="s">
+      <c r="B91" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J91" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="92" spans="2:10" ht="15" customHeight="1">
+      <c r="B92" s="17" t="s">
+        <v>163</v>
+      </c>
+      <c r="C92" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D92" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E92" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F92" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G92" s="18">
+        <v>-2.731162919997587</v>
+      </c>
+      <c r="H92" s="19">
+        <v>-0.00020651657828418788</v>
+      </c>
+      <c r="I92" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="J92" s="20" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="93" spans="2:10" ht="15" customHeight="1">
+      <c r="B93" s="17" t="s">
+        <v>164</v>
+      </c>
+      <c r="C93" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D93" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E93" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F93" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G93" s="18">
+        <v>13224.90883148</v>
+      </c>
+      <c r="H93" s="19">
+        <v>0.999999999997016</v>
+      </c>
+      <c r="I93" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="J93" s="20" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="95" spans="2:8" ht="15" customHeight="1">
+      <c r="B95" s="18" t="s">
         <v>165</v>
       </c>
-      <c r="C91" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D91" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E91" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F91" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G91" s="9">
-        <v>349.9999944</v>
-      </c>
-      <c r="H91" s="10">
-        <v>0.0299455345268</v>
-      </c>
-      <c r="I91" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J91" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="92" spans="2:10" ht="15" customHeight="1">
-      <c r="B92" s="12" t="s">
+      <c r="C95" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D95" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E95" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F95" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G95" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="H95" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="96" spans="2:8" ht="15" customHeight="1">
+      <c r="B96" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="C96" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="D96" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="E96" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="F96" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="G96" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="H96" s="18" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="97" spans="2:8" ht="15" customHeight="1">
+      <c r="B97" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="C92" s="13"/>
-      <c r="D92" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E92" s="13"/>
-      <c r="G92" s="15">
-        <v>349.9999944</v>
-      </c>
-      <c r="H92" s="16">
-        <v>0.0299455345268</v>
-      </c>
-      <c r="I92" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J92" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="93" spans="2:10" ht="15" customHeight="1">
-      <c r="B93" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J93" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="94" spans="2:10" ht="15" customHeight="1">
-      <c r="B94" s="17" t="s">
+      <c r="C97" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D97" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E97" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F97" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G97" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H97" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="98" spans="2:10" ht="15" customHeight="1">
+      <c r="B98" s="12" t="s">
         <v>167</v>
       </c>
-      <c r="C94" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D94" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="E94" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F94" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G94" s="18">
-        <v>7.836026990004029</v>
-      </c>
-      <c r="H94" s="19">
-        <v>0.0006704400586781319</v>
-      </c>
-      <c r="I94" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="J94" s="20" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="95" spans="2:10" ht="15" customHeight="1">
-      <c r="B95" s="17" t="s">
+      <c r="C98" s="13"/>
+      <c r="D98" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E98" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="F98" s="14">
+        <v>18900</v>
+      </c>
+      <c r="G98" s="15">
+        <v>275.05</v>
+      </c>
+      <c r="H98" s="16">
+        <v>0.0207978749422</v>
+      </c>
+      <c r="I98" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="J98" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="102" spans="2:9" ht="15" customHeight="1">
+      <c r="B102" s="13" t="s">
         <v>168</v>
       </c>
-      <c r="C95" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D95" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="E95" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F95" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G95" s="18">
-        <v>11687.88602139</v>
-      </c>
-      <c r="H95" s="19">
-        <v>0.9999999999973784</v>
-      </c>
-      <c r="I95" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="J95" s="20" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="97" spans="2:8" ht="15" customHeight="1">
-      <c r="B97" s="18" t="s">
+      <c r="C102" s="21"/>
+      <c r="D102" s="21"/>
+      <c r="E102" s="21"/>
+      <c r="F102" s="21"/>
+      <c r="G102" s="21"/>
+      <c r="H102" s="21"/>
+      <c r="I102" s="21"/>
+    </row>
+    <row r="106" spans="2:9" ht="15" customHeight="1">
+      <c r="B106" s="13" t="s">
         <v>169</v>
       </c>
-      <c r="C97" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D97" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="E97" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F97" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G97" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="H97" s="18" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="98" spans="2:8" ht="15" customHeight="1">
-      <c r="B98" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="C98" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="D98" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="E98" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="F98" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="G98" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="H98" s="18" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="99" spans="2:8" ht="15" customHeight="1">
-      <c r="B99" s="7" t="s">
+      <c r="C106" s="21"/>
+      <c r="D106" s="21"/>
+      <c r="E106" s="21"/>
+      <c r="F106" s="21"/>
+      <c r="G106" s="21"/>
+      <c r="H106" s="21"/>
+      <c r="I106" s="21"/>
+    </row>
+    <row r="107" spans="2:8" ht="15" customHeight="1">
+      <c r="B107" s="13" t="s">
         <v>170</v>
       </c>
-      <c r="C99" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D99" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E99" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F99" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G99" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H99" s="8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="100" spans="2:10" ht="15" customHeight="1">
-      <c r="B100" s="12" t="s">
+      <c r="C107" s="21"/>
+      <c r="D107" s="21"/>
+      <c r="E107" s="21"/>
+      <c r="F107" s="21"/>
+      <c r="G107" s="21"/>
+      <c r="H107" s="21"/>
+    </row>
+    <row r="108" spans="2:8" ht="15" customHeight="1">
+      <c r="B108" s="13" t="s">
         <v>171</v>
-      </c>
-      <c r="C100" s="13"/>
-      <c r="D100" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E100" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="F100" s="14">
-        <v>18900</v>
-      </c>
-      <c r="G100" s="15">
-        <v>237.66</v>
-      </c>
-      <c r="H100" s="16">
-        <v>0.0203338738558</v>
-      </c>
-      <c r="I100" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J100" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="104" spans="2:9" ht="15" customHeight="1">
-      <c r="B104" s="13" t="s">
-        <v>172</v>
-      </c>
-      <c r="C104" s="21"/>
-      <c r="D104" s="21"/>
-      <c r="E104" s="21"/>
-      <c r="F104" s="21"/>
-      <c r="G104" s="21"/>
-      <c r="H104" s="21"/>
-      <c r="I104" s="21"/>
-    </row>
-    <row r="108" spans="2:9" ht="15" customHeight="1">
-      <c r="B108" s="13" t="s">
-        <v>173</v>
       </c>
       <c r="C108" s="21"/>
       <c r="D108" s="21"/>
@@ -3803,11 +3756,10 @@
       <c r="F108" s="21"/>
       <c r="G108" s="21"/>
       <c r="H108" s="21"/>
-      <c r="I108" s="21"/>
-    </row>
-    <row r="109" spans="2:8" ht="15" customHeight="1">
-      <c r="B109" s="13" t="s">
-        <v>174</v>
+    </row>
+    <row r="109" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B109" s="22" t="s">
+        <v>172</v>
       </c>
       <c r="C109" s="21"/>
       <c r="D109" s="21"/>
@@ -3816,9 +3768,9 @@
       <c r="G109" s="21"/>
       <c r="H109" s="21"/>
     </row>
-    <row r="110" spans="2:8" ht="15" customHeight="1">
-      <c r="B110" s="13" t="s">
-        <v>175</v>
+    <row r="110" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B110" s="22" t="s">
+        <v>173</v>
       </c>
       <c r="C110" s="21"/>
       <c r="D110" s="21"/>
@@ -3829,7 +3781,7 @@
     </row>
     <row r="111" spans="2:8" ht="27.6" customHeight="1">
       <c r="B111" s="22" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C111" s="21"/>
       <c r="D111" s="21"/>
@@ -3838,55 +3790,33 @@
       <c r="G111" s="21"/>
       <c r="H111" s="21"/>
     </row>
-    <row r="112" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B112" s="22" t="s">
+    <row r="114" ht="15">
+      <c r="B114" s="21" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="129" ht="15">
+      <c r="B129" s="21" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="130" ht="15">
+      <c r="B130" s="21" t="s">
         <v>177</v>
-      </c>
-      <c r="C112" s="21"/>
-      <c r="D112" s="21"/>
-      <c r="E112" s="21"/>
-      <c r="F112" s="21"/>
-      <c r="G112" s="21"/>
-      <c r="H112" s="21"/>
-    </row>
-    <row r="113" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B113" s="22" t="s">
-        <v>178</v>
-      </c>
-      <c r="C113" s="21"/>
-      <c r="D113" s="21"/>
-      <c r="E113" s="21"/>
-      <c r="F113" s="21"/>
-      <c r="G113" s="21"/>
-      <c r="H113" s="21"/>
-    </row>
-    <row r="116" ht="15">
-      <c r="B116" s="21" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="131" ht="15">
-      <c r="B131" s="21" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="132" ht="15">
-      <c r="B132" s="21" t="s">
-        <v>181</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B107:H107"/>
+    <mergeCell ref="B108:H108"/>
     <mergeCell ref="B109:H109"/>
     <mergeCell ref="B110:H110"/>
     <mergeCell ref="B111:H111"/>
-    <mergeCell ref="B112:H112"/>
-    <mergeCell ref="B113:H113"/>
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B104:I104"/>
-    <mergeCell ref="B108:I108"/>
+    <mergeCell ref="B102:I102"/>
+    <mergeCell ref="B106:I106"/>
   </mergeCells>
   <printOptions gridLines="1" headings="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
